--- a/results/Int Task Remove ACC -0.4/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.4/Linea_fi_explain.xlsx
@@ -1166,13 +1166,13 @@
         <v>0.0471131587414526</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0009945096359292871</v>
+        <v>-0.001003977424180008</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006858094056078401</v>
+        <v>0.0006827617850463453</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03721138196688344</v>
+        <v>0.03720501531028911</v>
       </c>
       <c r="K3" t="n">
         <v>0.02403274390917505</v>
@@ -1187,7 +1187,7 @@
         <v>0.009289680591739076</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03461369617608519</v>
+        <v>0.03461053362074048</v>
       </c>
       <c r="P3" t="n">
         <v>0.01041278630550586</v>
@@ -1196,7 +1196,7 @@
         <v>0.01352637649857377</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01335138406116644</v>
+        <v>0.01335423139713318</v>
       </c>
       <c r="S3" t="n">
         <v>0.3088923764026981</v>
@@ -1208,7 +1208,7 @@
         <v>0.1306575349447426</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0006766505989898575</v>
+        <v>0.0006796763175980269</v>
       </c>
       <c r="W3" t="n">
         <v>0.007330366927428049</v>
@@ -1289,7 +1289,7 @@
         <v>0.005049197534181037</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0005873282471278065</v>
+        <v>0.0005933019627789415</v>
       </c>
       <c r="AX3" t="n">
         <v>0.0007118535788026448</v>
@@ -1355,7 +1355,7 @@
         <v>-0.0018638926630939</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.002630219939100135</v>
+        <v>0.002630140252920796</v>
       </c>
       <c r="BT3" t="n">
         <v>0.0007791722346015915</v>
@@ -1437,13 +1437,13 @@
         <v>0.06679980853170039</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00358876791692905</v>
+        <v>0.003588459151648663</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0009515978391204362</v>
+        <v>0.0009502648929812674</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04922733955435524</v>
+        <v>0.04922180645092275</v>
       </c>
       <c r="K4" t="n">
         <v>0.02253009439346159</v>
@@ -1458,7 +1458,7 @@
         <v>0.02080722397109335</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04820318691296765</v>
+        <v>0.04819731669906484</v>
       </c>
       <c r="P4" t="n">
         <v>0.01635988898586188</v>
@@ -1467,7 +1467,7 @@
         <v>0.02445356942277206</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02274085345683801</v>
+        <v>0.0227395474158583</v>
       </c>
       <c r="S4" t="n">
         <v>0.1161024062062815</v>
@@ -1479,7 +1479,7 @@
         <v>0.06312323503651079</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0009547240215101073</v>
+        <v>0.0009509968773516624</v>
       </c>
       <c r="W4" t="n">
         <v>0.01174826228104876</v>
@@ -1560,7 +1560,7 @@
         <v>0.01333487228399433</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.02071304557231596</v>
+        <v>0.02070131004933163</v>
       </c>
       <c r="AX4" t="n">
         <v>0.00398684803460081</v>
@@ -1626,7 +1626,7 @@
         <v>0.008811423776286137</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.008608280236610375</v>
+        <v>0.008612512086360465</v>
       </c>
       <c r="BT4" t="n">
         <v>0.003440564866773353</v>
@@ -1750,7 +1750,7 @@
         <v>0.009128754088611324</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0003933434190620311</v>
+        <v>-0.0003630862329803364</v>
       </c>
       <c r="W5" t="n">
         <v>-0.01618876941457582</v>
@@ -1831,7 +1831,7 @@
         <v>-0.004462602137020722</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.0360513739545997</v>
+        <v>-0.03599163679808835</v>
       </c>
       <c r="AX5" t="n">
         <v>-0.005567322239031813</v>
@@ -1979,7 +1979,7 @@
         <v>0.007403886107200819</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.001949723983194407</v>
+        <v>-0.001965536759918002</v>
       </c>
       <c r="I6" t="n">
         <v>-7.698658837387847e-06</v>
@@ -2009,7 +2009,7 @@
         <v>-0.0001631600031763657</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002429675549518057</v>
+        <v>0.002429675549518059</v>
       </c>
       <c r="S6" t="n">
         <v>0.2481681471270377</v>
@@ -2253,10 +2253,10 @@
         <v>-0.0009696070523674439</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0004852929737971301</v>
+        <v>0.0005007203110387215</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01077323058234657</v>
+        <v>0.01075721007609857</v>
       </c>
       <c r="K7" t="n">
         <v>0.0255544784182349</v>
@@ -2280,7 +2280,7 @@
         <v>0.01323718725250574</v>
       </c>
       <c r="R7" t="n">
-        <v>0.004392914912934203</v>
+        <v>0.0044071515927679</v>
       </c>
       <c r="S7" t="n">
         <v>0.2932328441633424</v>
@@ -2439,7 +2439,7 @@
         <v>-0.0003814102581961521</v>
       </c>
       <c r="BS7" t="n">
-        <v>-4.646320242937542e-05</v>
+        <v>-6.179592245390554e-05</v>
       </c>
       <c r="BT7" t="n">
         <v>0.001080101570710651</v>
@@ -2521,10 +2521,10 @@
         <v>0.04988778559346408</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0005324247302574748</v>
+        <v>0.0005245680363542671</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009957026245288048</v>
+        <v>0.0009803699045042719</v>
       </c>
       <c r="J8" t="n">
         <v>0.0536867098915036</v>
@@ -2798,7 +2798,7 @@
         <v>0.002545568824638622</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1397216951296648</v>
+        <v>0.1396900695762176</v>
       </c>
       <c r="K9" t="n">
         <v>0.05482602118003022</v>
